--- a/challan_export.xlsx
+++ b/challan_export.xlsx
@@ -11,11 +11,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="251">
   <si>
     <t xml:space="preserve">SNo</t>
   </si>
   <si>
+    <t xml:space="preserve">Invoice Challan Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoice Challan Date</t>
+  </si>
+  <si>
     <t xml:space="preserve">Challan Number</t>
   </si>
   <si>
@@ -32,6 +38,732 @@
   </si>
   <si>
     <t xml:space="preserve">Staff Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1234567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 July 2026: 03:04 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAE-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prince Art Export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shayam  Jangid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 July 2026: 02:17 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMATPL-137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUNCITY METALS AND TUBES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 July 2026: 02:13 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhandari Exports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 July 2026: 02:07 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAE-139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAR ART EXPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIT FIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 July 2026: 11:40 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BHANDU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 July 2026: 03:31 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAE-171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANSAL  ART EXPORT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 July 2026: 02:55 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHAPLT-95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEACHTREE HOME ACCENTS Pvt Ltd Tanawara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 July 2026: 02:53 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC-49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heritage Creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 July 2026: 01:16 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMPC-125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shree Mukesh Plywood Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 July 2026: 11:10 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RH(PSN-110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISHABH HANDICRAFT ( PARTNER SHIP) NEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 July 2026: 10:59 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REPL-109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishabh Expocrafts Private Limited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 July 2026: 03:26 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AACI-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art And Craft Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JET FURNITURE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 July 2026: 01:54 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BHAVAL EXPORTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 July 2026: 11:41 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIL-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVERGREEN INTERNATIONAL LTD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 July 2026: 11:19 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPPL-101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prins Polytech Private Limited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 July 2026: 11:12 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNPURNA INDUSTRIES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 July 2026: 03:29 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHA(LB-96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peachtree Home Accounts (P) Ltd Basni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 July 2026: 02:22 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 July 2026: 12:35 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFINITY INDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 July 2026: 12:28 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHFB-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambiance Home Furnising Boranada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 July 2026: 12:25 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA&amp;D-193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lila Art &amp;Crafts    Dangiawas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 July 2026: 12:20 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS-82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marwar Supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 July 2026: 02:25 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NP-167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK PACKERS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 July 2026: 02:11 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC-57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIAN CRAFTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 July 2026: 12:31 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNH-126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHREE NAKODA HARDWARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pawan  Shah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 July 2026: 03:49 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIT ONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 July 2026: 02:12 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPH-142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE PACKAGING HOUSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 July 2026: 02:09 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SME(P-124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shree Mahadev Enterprises (TEJARAM PATEL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 July 2026: 11:31 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KE-157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kingdom Export </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 July 2026: 05:43 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VBPL-186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vikas Bikes PVT LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 July 2026: 05:39 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAB-174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VINAYAK AUTO BARMER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 July 2026: 02:09 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAFPL-199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annkoot Agro Food PVT LTD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 July 2026: 10:06 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAAC-67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jodhana Art And Crafts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 July 2026: 04:58 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D.P.S. MARKETING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 July 2026: 02:26 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAE-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aditi Art Export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 July 2026: 02:15 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TA-188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE ATTIC   Karaftourim </t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 July 2026: 05:09 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSI-51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOME SENSE INTERNATIONAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 July 2026: 01:58 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 July 2026: 05:19 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 July 2026: 05:11 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 July 2026: 04:56 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFP-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contemporary Furniture Pvt.Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trilok Ji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 July 2026: 02:29 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 July 2026: 11:44 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 July 2026: 11:40 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 July 2026: 11:36 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RI-104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAJLAXMI INDUSTRIES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 July 2026: 01:50 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahendra Industries </t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 July 2026: 05:54 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC-98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prakash Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 July 2026: 02:56 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTF-414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 July 2026: 02:46 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mayank Export</t>
   </si>
 </sst>
 </file>
@@ -300,6 +1032,1462 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
